--- a/ProgramarePentruStiinteAplicate2/Prezenta Programare.xlsx
+++ b/ProgramarePentruStiinteAplicate2/Prezenta Programare.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\remus\Documents\GitHub\Geoinformatica_Promotia_2025_2028\ASDII_si_PSAII\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\remus\Documents\GitHub\Geoinformatica_Promotia_2025_2028\ProgramarePentruStiinteAplicate2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1B4ADC8-C7E5-4D22-9C7E-3B196D9BFD4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65F181A7-2BEE-424F-950E-32B06B740C2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -741,7 +741,9 @@
       <c r="C3" s="5">
         <v>2</v>
       </c>
-      <c r="D3" s="6"/>
+      <c r="D3" s="6">
+        <v>2</v>
+      </c>
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
@@ -756,7 +758,7 @@
       <c r="P3" s="7"/>
       <c r="Q3" s="8">
         <f t="shared" ref="Q3:Q22" si="0">SUM(C3:P3)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R3" s="7"/>
     </row>
@@ -843,10 +845,13 @@
       <c r="C10" s="9">
         <v>2</v>
       </c>
+      <c r="D10" s="3">
+        <v>2</v>
+      </c>
       <c r="P10" s="10"/>
       <c r="Q10" s="8">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R10" s="10"/>
     </row>
@@ -855,10 +860,13 @@
         <v>19</v>
       </c>
       <c r="C11" s="9"/>
+      <c r="D11" s="3">
+        <v>2</v>
+      </c>
       <c r="P11" s="10"/>
       <c r="Q11" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R11" s="10"/>
     </row>
@@ -881,10 +889,13 @@
       <c r="C13" s="9">
         <v>2</v>
       </c>
+      <c r="D13" s="3">
+        <v>2</v>
+      </c>
       <c r="P13" s="10"/>
       <c r="Q13" s="8">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R13" s="10"/>
     </row>
@@ -909,10 +920,13 @@
       <c r="C15" s="9">
         <v>2</v>
       </c>
+      <c r="D15" s="3">
+        <v>2</v>
+      </c>
       <c r="P15" s="10"/>
       <c r="Q15" s="8">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R15" s="10"/>
     </row>
@@ -963,10 +977,13 @@
       <c r="C19" s="9">
         <v>2</v>
       </c>
+      <c r="D19" s="3">
+        <v>2</v>
+      </c>
       <c r="P19" s="10"/>
       <c r="Q19" s="8">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R19" s="10"/>
     </row>
@@ -975,10 +992,13 @@
         <v>26</v>
       </c>
       <c r="C20" s="9"/>
+      <c r="D20" s="3">
+        <v>2</v>
+      </c>
       <c r="P20" s="10"/>
       <c r="Q20" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R20" s="10"/>
     </row>
@@ -1001,10 +1021,13 @@
       <c r="C22" s="9">
         <v>2</v>
       </c>
+      <c r="D22" s="3">
+        <v>2</v>
+      </c>
       <c r="P22" s="10"/>
       <c r="Q22" s="8">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R22" s="10"/>
     </row>

--- a/ProgramarePentruStiinteAplicate2/Prezenta Programare.xlsx
+++ b/ProgramarePentruStiinteAplicate2/Prezenta Programare.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\remus\Documents\GitHub\Geoinformatica_Promotia_2025_2028\ProgramarePentruStiinteAplicate2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65F181A7-2BEE-424F-950E-32B06B740C2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98F01075-E606-4493-827E-3DAB46A12EA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -744,7 +744,9 @@
       <c r="D3" s="6">
         <v>2</v>
       </c>
-      <c r="E3" s="6"/>
+      <c r="E3" s="6">
+        <v>2</v>
+      </c>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
       <c r="H3" s="6"/>
@@ -758,7 +760,7 @@
       <c r="P3" s="7"/>
       <c r="Q3" s="8">
         <f t="shared" ref="Q3:Q22" si="0">SUM(C3:P3)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R3" s="7"/>
     </row>
@@ -767,10 +769,13 @@
         <v>25</v>
       </c>
       <c r="C4" s="9"/>
+      <c r="E4" s="3">
+        <v>2</v>
+      </c>
       <c r="P4" s="10"/>
       <c r="Q4" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R4" s="10"/>
     </row>
@@ -831,10 +836,13 @@
       <c r="C9" s="9">
         <v>2</v>
       </c>
+      <c r="E9" s="3">
+        <v>2</v>
+      </c>
       <c r="P9" s="10"/>
       <c r="Q9" s="8">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R9" s="10"/>
     </row>
@@ -848,10 +856,13 @@
       <c r="D10" s="3">
         <v>2</v>
       </c>
+      <c r="E10" s="3">
+        <v>2</v>
+      </c>
       <c r="P10" s="10"/>
       <c r="Q10" s="8">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R10" s="10"/>
     </row>
@@ -875,10 +886,13 @@
         <v>24</v>
       </c>
       <c r="C12" s="9"/>
+      <c r="E12" s="3">
+        <v>2</v>
+      </c>
       <c r="P12" s="10"/>
       <c r="Q12" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R12" s="10"/>
     </row>
@@ -892,10 +906,13 @@
       <c r="D13" s="3">
         <v>2</v>
       </c>
+      <c r="E13" s="3">
+        <v>2</v>
+      </c>
       <c r="P13" s="10"/>
       <c r="Q13" s="8">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R13" s="10"/>
     </row>
@@ -923,10 +940,13 @@
       <c r="D15" s="3">
         <v>2</v>
       </c>
+      <c r="E15" s="3">
+        <v>2</v>
+      </c>
       <c r="P15" s="10"/>
       <c r="Q15" s="8">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R15" s="10"/>
     </row>
@@ -995,10 +1015,13 @@
       <c r="D20" s="3">
         <v>2</v>
       </c>
+      <c r="E20" s="3">
+        <v>2</v>
+      </c>
       <c r="P20" s="10"/>
       <c r="Q20" s="8">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R20" s="10"/>
     </row>
@@ -1024,10 +1047,13 @@
       <c r="D22" s="3">
         <v>2</v>
       </c>
+      <c r="E22" s="3">
+        <v>2</v>
+      </c>
       <c r="P22" s="10"/>
       <c r="Q22" s="8">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R22" s="10"/>
     </row>

--- a/ProgramarePentruStiinteAplicate2/Prezenta Programare.xlsx
+++ b/ProgramarePentruStiinteAplicate2/Prezenta Programare.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\remus\Documents\GitHub\Geoinformatica_Promotia_2025_2028\ProgramarePentruStiinteAplicate2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98F01075-E606-4493-827E-3DAB46A12EA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ABE33F0-0BA1-4257-B218-B9E4C270D1AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -747,7 +747,9 @@
       <c r="E3" s="6">
         <v>2</v>
       </c>
-      <c r="F3" s="6"/>
+      <c r="F3" s="6">
+        <v>2</v>
+      </c>
       <c r="G3" s="6"/>
       <c r="H3" s="6"/>
       <c r="I3" s="6"/>
@@ -760,7 +762,7 @@
       <c r="P3" s="7"/>
       <c r="Q3" s="8">
         <f t="shared" ref="Q3:Q22" si="0">SUM(C3:P3)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R3" s="7"/>
     </row>
@@ -772,10 +774,13 @@
       <c r="E4" s="3">
         <v>2</v>
       </c>
+      <c r="F4" s="3">
+        <v>2</v>
+      </c>
       <c r="P4" s="10"/>
       <c r="Q4" s="8">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R4" s="10"/>
     </row>
@@ -839,10 +844,13 @@
       <c r="E9" s="3">
         <v>2</v>
       </c>
+      <c r="F9" s="3">
+        <v>2</v>
+      </c>
       <c r="P9" s="10"/>
       <c r="Q9" s="8">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R9" s="10"/>
     </row>
@@ -889,10 +897,13 @@
       <c r="E12" s="3">
         <v>2</v>
       </c>
+      <c r="F12" s="3">
+        <v>2</v>
+      </c>
       <c r="P12" s="10"/>
       <c r="Q12" s="8">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R12" s="10"/>
     </row>
@@ -909,10 +920,13 @@
       <c r="E13" s="3">
         <v>2</v>
       </c>
+      <c r="F13" s="3">
+        <v>2</v>
+      </c>
       <c r="P13" s="10"/>
       <c r="Q13" s="8">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R13" s="10"/>
     </row>
@@ -943,10 +957,13 @@
       <c r="E15" s="3">
         <v>2</v>
       </c>
+      <c r="F15" s="3">
+        <v>2</v>
+      </c>
       <c r="P15" s="10"/>
       <c r="Q15" s="8">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R15" s="10"/>
     </row>
@@ -955,10 +972,13 @@
         <v>23</v>
       </c>
       <c r="C16" s="9"/>
+      <c r="F16" s="3">
+        <v>2</v>
+      </c>
       <c r="P16" s="10"/>
       <c r="Q16" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R16" s="10"/>
     </row>
@@ -1018,10 +1038,13 @@
       <c r="E20" s="3">
         <v>2</v>
       </c>
+      <c r="F20" s="3">
+        <v>2</v>
+      </c>
       <c r="P20" s="10"/>
       <c r="Q20" s="8">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R20" s="10"/>
     </row>
@@ -1050,10 +1073,13 @@
       <c r="E22" s="3">
         <v>2</v>
       </c>
+      <c r="F22" s="3">
+        <v>2</v>
+      </c>
       <c r="P22" s="10"/>
       <c r="Q22" s="8">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R22" s="10"/>
     </row>

--- a/ProgramarePentruStiinteAplicate2/Prezenta Programare.xlsx
+++ b/ProgramarePentruStiinteAplicate2/Prezenta Programare.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\remus\Documents\GitHub\Geoinformatica_Promotia_2025_2028\ProgramarePentruStiinteAplicate2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ABE33F0-0BA1-4257-B218-B9E4C270D1AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39183DBE-5ACD-42C6-9516-4DE032D80957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -750,7 +750,9 @@
       <c r="F3" s="6">
         <v>2</v>
       </c>
-      <c r="G3" s="6"/>
+      <c r="G3" s="6">
+        <v>2</v>
+      </c>
       <c r="H3" s="6"/>
       <c r="I3" s="6"/>
       <c r="J3" s="6"/>
@@ -762,7 +764,7 @@
       <c r="P3" s="7"/>
       <c r="Q3" s="8">
         <f t="shared" ref="Q3:Q22" si="0">SUM(C3:P3)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R3" s="7"/>
     </row>
@@ -867,10 +869,13 @@
       <c r="E10" s="3">
         <v>2</v>
       </c>
+      <c r="G10" s="3">
+        <v>2</v>
+      </c>
       <c r="P10" s="10"/>
       <c r="Q10" s="8">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R10" s="10"/>
     </row>
@@ -882,10 +887,13 @@
       <c r="D11" s="3">
         <v>2</v>
       </c>
+      <c r="G11" s="3">
+        <v>2</v>
+      </c>
       <c r="P11" s="10"/>
       <c r="Q11" s="8">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R11" s="10"/>
     </row>
@@ -923,10 +931,13 @@
       <c r="F13" s="3">
         <v>2</v>
       </c>
+      <c r="G13" s="3">
+        <v>2</v>
+      </c>
       <c r="P13" s="10"/>
       <c r="Q13" s="8">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R13" s="10"/>
     </row>
@@ -960,10 +971,13 @@
       <c r="F15" s="3">
         <v>2</v>
       </c>
+      <c r="G15" s="3">
+        <v>2</v>
+      </c>
       <c r="P15" s="10"/>
       <c r="Q15" s="8">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R15" s="10"/>
     </row>
@@ -1076,10 +1090,13 @@
       <c r="F22" s="3">
         <v>2</v>
       </c>
+      <c r="G22" s="3">
+        <v>2</v>
+      </c>
       <c r="P22" s="10"/>
       <c r="Q22" s="8">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R22" s="10"/>
     </row>

--- a/ProgramarePentruStiinteAplicate2/Prezenta Programare.xlsx
+++ b/ProgramarePentruStiinteAplicate2/Prezenta Programare.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\remus\Documents\GitHub\Geoinformatica_Promotia_2025_2028\ProgramarePentruStiinteAplicate2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39183DBE-5ACD-42C6-9516-4DE032D80957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4848FC6F-0462-43A7-BC48-32D84A0A4984}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1003,10 +1003,13 @@
       <c r="C17" s="9">
         <v>2</v>
       </c>
+      <c r="H17" s="3">
+        <v>2</v>
+      </c>
       <c r="P17" s="10"/>
       <c r="Q17" s="8">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R17" s="10"/>
     </row>
@@ -1017,10 +1020,13 @@
       <c r="C18" s="9">
         <v>2</v>
       </c>
+      <c r="H18" s="3">
+        <v>2</v>
+      </c>
       <c r="P18" s="10"/>
       <c r="Q18" s="8">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R18" s="10"/>
     </row>
@@ -1055,10 +1061,13 @@
       <c r="F20" s="3">
         <v>2</v>
       </c>
+      <c r="H20" s="3">
+        <v>2</v>
+      </c>
       <c r="P20" s="10"/>
       <c r="Q20" s="8">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R20" s="10"/>
     </row>
@@ -1093,10 +1102,13 @@
       <c r="G22" s="3">
         <v>2</v>
       </c>
+      <c r="H22" s="3">
+        <v>2</v>
+      </c>
       <c r="P22" s="10"/>
       <c r="Q22" s="8">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="R22" s="10"/>
     </row>

--- a/ProgramarePentruStiinteAplicate2/Prezenta Programare.xlsx
+++ b/ProgramarePentruStiinteAplicate2/Prezenta Programare.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\remus\Documents\GitHub\Geoinformatica_Promotia_2025_2028\ProgramarePentruStiinteAplicate2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4848FC6F-0462-43A7-BC48-32D84A0A4984}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{229553E2-96BF-46A7-A3C5-029849C94166}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -872,10 +872,13 @@
       <c r="G10" s="3">
         <v>2</v>
       </c>
+      <c r="I10" s="3">
+        <v>2</v>
+      </c>
       <c r="P10" s="10"/>
       <c r="Q10" s="8">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R10" s="10"/>
     </row>
@@ -934,10 +937,13 @@
       <c r="G13" s="3">
         <v>2</v>
       </c>
+      <c r="I13" s="3">
+        <v>2</v>
+      </c>
       <c r="P13" s="10"/>
       <c r="Q13" s="8">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="R13" s="10"/>
     </row>
@@ -1064,10 +1070,13 @@
       <c r="H20" s="3">
         <v>2</v>
       </c>
+      <c r="I20" s="3">
+        <v>2</v>
+      </c>
       <c r="P20" s="10"/>
       <c r="Q20" s="8">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R20" s="10"/>
     </row>
@@ -1105,10 +1114,13 @@
       <c r="H22" s="3">
         <v>2</v>
       </c>
+      <c r="I22" s="3">
+        <v>2</v>
+      </c>
       <c r="P22" s="10"/>
       <c r="Q22" s="8">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="R22" s="10"/>
     </row>

--- a/ProgramarePentruStiinteAplicate2/Prezenta Programare.xlsx
+++ b/ProgramarePentruStiinteAplicate2/Prezenta Programare.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\remus\Documents\GitHub\Geoinformatica_Promotia_2025_2028\ProgramarePentruStiinteAplicate2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{229553E2-96BF-46A7-A3C5-029849C94166}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1496FFC0-0BDC-47A1-9A6F-6EE0EE0E4D19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -755,7 +755,9 @@
       </c>
       <c r="H3" s="6"/>
       <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
+      <c r="J3" s="6">
+        <v>2</v>
+      </c>
       <c r="K3" s="6"/>
       <c r="L3" s="6"/>
       <c r="M3" s="6"/>
@@ -764,7 +766,7 @@
       <c r="P3" s="7"/>
       <c r="Q3" s="8">
         <f t="shared" ref="Q3:Q22" si="0">SUM(C3:P3)</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="R3" s="7"/>
     </row>
@@ -849,10 +851,13 @@
       <c r="F9" s="3">
         <v>2</v>
       </c>
+      <c r="J9" s="3">
+        <v>2</v>
+      </c>
       <c r="P9" s="10"/>
       <c r="Q9" s="8">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R9" s="10"/>
     </row>
@@ -875,10 +880,13 @@
       <c r="I10" s="3">
         <v>2</v>
       </c>
+      <c r="J10" s="3">
+        <v>2</v>
+      </c>
       <c r="P10" s="10"/>
       <c r="Q10" s="8">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="R10" s="10"/>
     </row>
@@ -940,10 +948,13 @@
       <c r="I13" s="3">
         <v>2</v>
       </c>
+      <c r="J13" s="3">
+        <v>2</v>
+      </c>
       <c r="P13" s="10"/>
       <c r="Q13" s="8">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="R13" s="10"/>
     </row>
@@ -980,10 +991,13 @@
       <c r="G15" s="3">
         <v>2</v>
       </c>
+      <c r="J15" s="3">
+        <v>2</v>
+      </c>
       <c r="P15" s="10"/>
       <c r="Q15" s="8">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="R15" s="10"/>
     </row>
@@ -1117,10 +1131,13 @@
       <c r="I22" s="3">
         <v>2</v>
       </c>
+      <c r="J22" s="3">
+        <v>2</v>
+      </c>
       <c r="P22" s="10"/>
       <c r="Q22" s="8">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="R22" s="10"/>
     </row>

--- a/ProgramarePentruStiinteAplicate2/Prezenta Programare.xlsx
+++ b/ProgramarePentruStiinteAplicate2/Prezenta Programare.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\remus\Documents\GitHub\Geoinformatica_Promotia_2025_2028\ProgramarePentruStiinteAplicate2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1496FFC0-0BDC-47A1-9A6F-6EE0EE0E4D19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14929C79-AAD4-4DEE-9455-5FE47D79FBB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -883,10 +883,13 @@
       <c r="J10" s="3">
         <v>2</v>
       </c>
+      <c r="K10" s="3">
+        <v>2</v>
+      </c>
       <c r="P10" s="10"/>
       <c r="Q10" s="8">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="R10" s="10"/>
     </row>
@@ -1134,10 +1137,13 @@
       <c r="J22" s="3">
         <v>2</v>
       </c>
+      <c r="K22" s="3">
+        <v>2</v>
+      </c>
       <c r="P22" s="10"/>
       <c r="Q22" s="8">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="R22" s="10"/>
     </row>

--- a/ProgramarePentruStiinteAplicate2/Prezenta Programare.xlsx
+++ b/ProgramarePentruStiinteAplicate2/Prezenta Programare.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\remus\Documents\GitHub\Geoinformatica_Promotia_2025_2028\ProgramarePentruStiinteAplicate2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14929C79-AAD4-4DEE-9455-5FE47D79FBB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D31E329-618F-4997-991C-09BED05D2591}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -954,10 +954,13 @@
       <c r="J13" s="3">
         <v>2</v>
       </c>
+      <c r="L13" s="3">
+        <v>2</v>
+      </c>
       <c r="P13" s="10"/>
       <c r="Q13" s="8">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="R13" s="10"/>
     </row>
@@ -997,10 +1000,13 @@
       <c r="J15" s="3">
         <v>2</v>
       </c>
+      <c r="L15" s="3">
+        <v>2</v>
+      </c>
       <c r="P15" s="10"/>
       <c r="Q15" s="8">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="R15" s="10"/>
     </row>

--- a/ProgramarePentruStiinteAplicate2/Prezenta Programare.xlsx
+++ b/ProgramarePentruStiinteAplicate2/Prezenta Programare.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\remus\Documents\GitHub\Geoinformatica_Promotia_2025_2028\ProgramarePentruStiinteAplicate2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D31E329-618F-4997-991C-09BED05D2591}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63CB27E8-553A-4830-A742-740C1034313D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -886,10 +886,13 @@
       <c r="K10" s="3">
         <v>2</v>
       </c>
+      <c r="N10" s="3">
+        <v>2</v>
+      </c>
       <c r="P10" s="10"/>
       <c r="Q10" s="8">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="R10" s="10"/>
     </row>
@@ -1052,10 +1055,13 @@
       <c r="H18" s="3">
         <v>2</v>
       </c>
+      <c r="N18" s="3">
+        <v>2</v>
+      </c>
       <c r="P18" s="10"/>
       <c r="Q18" s="8">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R18" s="10"/>
     </row>
